--- a/NBC_GYMNASTICS_2026-03-22_Girls_results.xlsx
+++ b/NBC_GYMNASTICS_2026-03-22_Girls_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mandbt-my.sharepoint.com/personal/cat_mandbt_onmicrosoft_com/Documents/NGL/22ND MARCH WEST MIDLANDS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{C6175732-F794-4901-B08A-1C2ED2C75EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED6331B9-4D42-4438-A273-9737F3194B75}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{C6175732-F794-4901-B08A-1C2ED2C75EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1776EB1-39F6-46CC-ABC0-5F6A76364AAB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="24">
   <si>
     <t>Club</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>Girls</t>
+  </si>
+  <si>
+    <t>12-14</t>
+  </si>
+  <si>
+    <t>15+</t>
   </si>
 </sst>
 </file>
@@ -455,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE7E3F99-9085-4F6A-B6A3-4430AF06C6C7}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
@@ -1363,6 +1369,934 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>4445114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29">
+        <v>10.4</v>
+      </c>
+      <c r="F29" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>4024041</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F30" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s">
+        <v>7</v>
+      </c>
+      <c r="I30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>3502681</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31">
+        <v>10.6</v>
+      </c>
+      <c r="F31" t="s">
+        <v>4</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>2264659</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32">
+        <v>11.4</v>
+      </c>
+      <c r="F32" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s">
+        <v>7</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>3833613</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33">
+        <v>10.7</v>
+      </c>
+      <c r="F33" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>7</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>3522006</v>
+      </c>
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34">
+        <v>10.4</v>
+      </c>
+      <c r="F34" t="s">
+        <v>4</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>4196689</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35">
+        <v>10.9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>4893603</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36">
+        <v>10.3</v>
+      </c>
+      <c r="F36" t="s">
+        <v>4</v>
+      </c>
+      <c r="G36" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" t="s">
+        <v>7</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>4567602</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F37" t="s">
+        <v>4</v>
+      </c>
+      <c r="G37" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" t="s">
+        <v>7</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>3231065</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38">
+        <v>11</v>
+      </c>
+      <c r="F38" t="s">
+        <v>4</v>
+      </c>
+      <c r="G38" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" t="s">
+        <v>7</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>4561901</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39">
+        <v>10.1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s">
+        <v>7</v>
+      </c>
+      <c r="I39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>3136586</v>
+      </c>
+      <c r="B40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F40" t="s">
+        <v>4</v>
+      </c>
+      <c r="G40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s">
+        <v>7</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>4009382</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41">
+        <v>10.6</v>
+      </c>
+      <c r="F41" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s">
+        <v>7</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>4830655</v>
+      </c>
+      <c r="B42" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42">
+        <v>10.4</v>
+      </c>
+      <c r="F42" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s">
+        <v>7</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>4998087</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43">
+        <v>11.3</v>
+      </c>
+      <c r="F43" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>3394191</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44">
+        <v>10.3</v>
+      </c>
+      <c r="F44" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" t="s">
+        <v>7</v>
+      </c>
+      <c r="I44" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>3336543</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45">
+        <v>10.7</v>
+      </c>
+      <c r="F45" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
+        <v>7</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>5178571</v>
+      </c>
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" t="s">
+        <v>6</v>
+      </c>
+      <c r="E46">
+        <v>10.4</v>
+      </c>
+      <c r="F46" t="s">
+        <v>4</v>
+      </c>
+      <c r="G46" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" t="s">
+        <v>7</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>3269799</v>
+      </c>
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47">
+        <v>11.6</v>
+      </c>
+      <c r="F47" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>3259308</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48">
+        <v>10.8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" t="s">
+        <v>7</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>2711051</v>
+      </c>
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49">
+        <v>11.4</v>
+      </c>
+      <c r="F49" t="s">
+        <v>4</v>
+      </c>
+      <c r="G49" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>4729019</v>
+      </c>
+      <c r="B50" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50">
+        <v>11</v>
+      </c>
+      <c r="F50" t="s">
+        <v>4</v>
+      </c>
+      <c r="G50" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" t="s">
+        <v>7</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>5144290</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51">
+        <v>9.9</v>
+      </c>
+      <c r="F51" t="s">
+        <v>4</v>
+      </c>
+      <c r="G51" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" t="s">
+        <v>7</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>2913678</v>
+      </c>
+      <c r="B52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52">
+        <v>10.7</v>
+      </c>
+      <c r="F52" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" t="s">
+        <v>7</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>4662464</v>
+      </c>
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F53" t="s">
+        <v>4</v>
+      </c>
+      <c r="G53" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" t="s">
+        <v>7</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>3641999</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54">
+        <v>10.4</v>
+      </c>
+      <c r="F54" t="s">
+        <v>4</v>
+      </c>
+      <c r="G54" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" t="s">
+        <v>7</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>3901702</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55">
+        <v>11.8</v>
+      </c>
+      <c r="F55" t="s">
+        <v>4</v>
+      </c>
+      <c r="G55" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>3841294</v>
+      </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56">
+        <v>10.6</v>
+      </c>
+      <c r="F56" t="s">
+        <v>4</v>
+      </c>
+      <c r="G56" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" t="s">
+        <v>7</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>4570286</v>
+      </c>
+      <c r="B57" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57">
+        <v>9.9</v>
+      </c>
+      <c r="F57" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" t="s">
+        <v>7</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>3146321</v>
+      </c>
+      <c r="B58" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58">
+        <v>10.5</v>
+      </c>
+      <c r="F58" t="s">
+        <v>4</v>
+      </c>
+      <c r="G58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" t="s">
+        <v>7</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>4582294</v>
+      </c>
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" t="s">
+        <v>6</v>
+      </c>
+      <c r="E59">
+        <v>10.1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" t="s">
+        <v>7</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>4249499</v>
+      </c>
+      <c r="B60" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60">
+        <v>10.8</v>
+      </c>
+      <c r="F60" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" t="s">
+        <v>11</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1370,7 +2304,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
@@ -2278,6 +3212,934 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>4445114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29">
+        <v>9.1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>4024041</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30">
+        <v>10.4</v>
+      </c>
+      <c r="F30" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s">
+        <v>7</v>
+      </c>
+      <c r="I30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>3502681</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31">
+        <v>11.4</v>
+      </c>
+      <c r="F31" t="s">
+        <v>4</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>2264659</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32">
+        <v>10.5</v>
+      </c>
+      <c r="F32" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s">
+        <v>7</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>3833613</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33">
+        <v>9.9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>7</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>3522006</v>
+      </c>
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34">
+        <v>10.3</v>
+      </c>
+      <c r="F34" t="s">
+        <v>4</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>4196689</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35">
+        <v>11.1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>4893603</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F36" t="s">
+        <v>4</v>
+      </c>
+      <c r="G36" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" t="s">
+        <v>7</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>4567602</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37">
+        <v>9.6</v>
+      </c>
+      <c r="F37" t="s">
+        <v>4</v>
+      </c>
+      <c r="G37" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" t="s">
+        <v>7</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>3231065</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38">
+        <v>10.7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>4</v>
+      </c>
+      <c r="G38" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" t="s">
+        <v>7</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>4561901</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="F39" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s">
+        <v>7</v>
+      </c>
+      <c r="I39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>3136586</v>
+      </c>
+      <c r="B40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40">
+        <v>10.8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>4</v>
+      </c>
+      <c r="G40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s">
+        <v>7</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>4009382</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41">
+        <v>8.6</v>
+      </c>
+      <c r="F41" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s">
+        <v>7</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>4830655</v>
+      </c>
+      <c r="B42" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42">
+        <v>10.1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s">
+        <v>7</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>4998087</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43">
+        <v>10.9</v>
+      </c>
+      <c r="F43" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>3394191</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F44" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" t="s">
+        <v>7</v>
+      </c>
+      <c r="I44" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>3336543</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F45" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
+        <v>7</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>5178571</v>
+      </c>
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" t="s">
+        <v>6</v>
+      </c>
+      <c r="E46">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="F46" t="s">
+        <v>4</v>
+      </c>
+      <c r="G46" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" t="s">
+        <v>7</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>3269799</v>
+      </c>
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47">
+        <v>11.2</v>
+      </c>
+      <c r="F47" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>3259308</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48">
+        <v>10</v>
+      </c>
+      <c r="F48" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" t="s">
+        <v>7</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>2711051</v>
+      </c>
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49">
+        <v>10.8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>4</v>
+      </c>
+      <c r="G49" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>4729019</v>
+      </c>
+      <c r="B50" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50">
+        <v>10</v>
+      </c>
+      <c r="F50" t="s">
+        <v>4</v>
+      </c>
+      <c r="G50" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" t="s">
+        <v>7</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>5144290</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51">
+        <v>9.9</v>
+      </c>
+      <c r="F51" t="s">
+        <v>4</v>
+      </c>
+      <c r="G51" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" t="s">
+        <v>7</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>2913678</v>
+      </c>
+      <c r="B52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52">
+        <v>10.8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" t="s">
+        <v>7</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>4662464</v>
+      </c>
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53">
+        <v>10.1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>4</v>
+      </c>
+      <c r="G53" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" t="s">
+        <v>7</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>3641999</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54">
+        <v>9</v>
+      </c>
+      <c r="F54" t="s">
+        <v>4</v>
+      </c>
+      <c r="G54" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" t="s">
+        <v>7</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>3901702</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55">
+        <v>11.4</v>
+      </c>
+      <c r="F55" t="s">
+        <v>4</v>
+      </c>
+      <c r="G55" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>3841294</v>
+      </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="F56" t="s">
+        <v>4</v>
+      </c>
+      <c r="G56" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" t="s">
+        <v>7</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>4570286</v>
+      </c>
+      <c r="B57" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F57" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" t="s">
+        <v>7</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>3146321</v>
+      </c>
+      <c r="B58" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="F58" t="s">
+        <v>4</v>
+      </c>
+      <c r="G58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" t="s">
+        <v>7</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>4582294</v>
+      </c>
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" t="s">
+        <v>6</v>
+      </c>
+      <c r="E59">
+        <v>10.4</v>
+      </c>
+      <c r="F59" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" t="s">
+        <v>7</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>4249499</v>
+      </c>
+      <c r="B60" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60">
+        <v>11.2</v>
+      </c>
+      <c r="F60" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" t="s">
+        <v>11</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2285,7 +4147,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B125325-26FC-431A-BC5D-45AE44FF3710}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
@@ -3193,6 +5055,934 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>4445114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29">
+        <v>11.4</v>
+      </c>
+      <c r="F29" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>4024041</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="F30" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s">
+        <v>7</v>
+      </c>
+      <c r="I30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>3502681</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31">
+        <v>11.8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>4</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>2264659</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32">
+        <v>10.9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s">
+        <v>7</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>3833613</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33">
+        <v>11.5</v>
+      </c>
+      <c r="F33" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>7</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>3522006</v>
+      </c>
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34">
+        <v>9.75</v>
+      </c>
+      <c r="F34" t="s">
+        <v>4</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>4196689</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35">
+        <v>11.5</v>
+      </c>
+      <c r="F35" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>4893603</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F36" t="s">
+        <v>4</v>
+      </c>
+      <c r="G36" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" t="s">
+        <v>7</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>4567602</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37">
+        <v>9.5</v>
+      </c>
+      <c r="F37" t="s">
+        <v>4</v>
+      </c>
+      <c r="G37" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" t="s">
+        <v>7</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>3231065</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38">
+        <v>11.8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>4</v>
+      </c>
+      <c r="G38" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" t="s">
+        <v>7</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>4561901</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39">
+        <v>11.15</v>
+      </c>
+      <c r="F39" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s">
+        <v>7</v>
+      </c>
+      <c r="I39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>3136586</v>
+      </c>
+      <c r="B40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40">
+        <v>9.1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>4</v>
+      </c>
+      <c r="G40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s">
+        <v>7</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>4009382</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41">
+        <v>10.5</v>
+      </c>
+      <c r="F41" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s">
+        <v>7</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>4830655</v>
+      </c>
+      <c r="B42" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42">
+        <v>11</v>
+      </c>
+      <c r="F42" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s">
+        <v>7</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>4998087</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43">
+        <v>11.3</v>
+      </c>
+      <c r="F43" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>3394191</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44">
+        <v>9.6</v>
+      </c>
+      <c r="F44" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" t="s">
+        <v>7</v>
+      </c>
+      <c r="I44" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>3336543</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45">
+        <v>10.8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
+        <v>7</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>5178571</v>
+      </c>
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" t="s">
+        <v>6</v>
+      </c>
+      <c r="E46">
+        <v>10.9</v>
+      </c>
+      <c r="F46" t="s">
+        <v>4</v>
+      </c>
+      <c r="G46" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" t="s">
+        <v>7</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>3269799</v>
+      </c>
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47">
+        <v>10.75</v>
+      </c>
+      <c r="F47" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>3259308</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48">
+        <v>10.9</v>
+      </c>
+      <c r="F48" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" t="s">
+        <v>7</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>2711051</v>
+      </c>
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49">
+        <v>11.3</v>
+      </c>
+      <c r="F49" t="s">
+        <v>4</v>
+      </c>
+      <c r="G49" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>4729019</v>
+      </c>
+      <c r="B50" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50">
+        <v>11.5</v>
+      </c>
+      <c r="F50" t="s">
+        <v>4</v>
+      </c>
+      <c r="G50" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" t="s">
+        <v>7</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>5144290</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51">
+        <v>10.8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>4</v>
+      </c>
+      <c r="G51" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" t="s">
+        <v>7</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>2913678</v>
+      </c>
+      <c r="B52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52">
+        <v>10.55</v>
+      </c>
+      <c r="F52" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" t="s">
+        <v>7</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>4662464</v>
+      </c>
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53">
+        <v>11.1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>4</v>
+      </c>
+      <c r="G53" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" t="s">
+        <v>7</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>3641999</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54">
+        <v>11</v>
+      </c>
+      <c r="F54" t="s">
+        <v>4</v>
+      </c>
+      <c r="G54" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" t="s">
+        <v>7</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>3901702</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="F55" t="s">
+        <v>4</v>
+      </c>
+      <c r="G55" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>3841294</v>
+      </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56">
+        <v>11.3</v>
+      </c>
+      <c r="F56" t="s">
+        <v>4</v>
+      </c>
+      <c r="G56" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" t="s">
+        <v>7</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>4570286</v>
+      </c>
+      <c r="B57" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57">
+        <v>9.35</v>
+      </c>
+      <c r="F57" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" t="s">
+        <v>7</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>3146321</v>
+      </c>
+      <c r="B58" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="F58" t="s">
+        <v>4</v>
+      </c>
+      <c r="G58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" t="s">
+        <v>7</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>4582294</v>
+      </c>
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" t="s">
+        <v>6</v>
+      </c>
+      <c r="E59">
+        <v>10.6</v>
+      </c>
+      <c r="F59" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" t="s">
+        <v>7</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>4249499</v>
+      </c>
+      <c r="B60" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60">
+        <v>11.5</v>
+      </c>
+      <c r="F60" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" t="s">
+        <v>11</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3200,7 +5990,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8C5914-1009-41F1-B90F-8016A07861A0}">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
@@ -4023,6 +6813,934 @@
         <v>21</v>
       </c>
     </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>4445114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29">
+        <v>11.1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>4024041</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s">
+        <v>7</v>
+      </c>
+      <c r="I30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>3502681</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31">
+        <v>12.7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>4</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>2264659</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s">
+        <v>7</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>3833613</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33">
+        <v>12.5</v>
+      </c>
+      <c r="F33" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>7</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>3522006</v>
+      </c>
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34">
+        <v>11.4</v>
+      </c>
+      <c r="F34" t="s">
+        <v>4</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>4196689</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35">
+        <v>12.2</v>
+      </c>
+      <c r="F35" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>4893603</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36">
+        <v>10.9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>4</v>
+      </c>
+      <c r="G36" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" t="s">
+        <v>7</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>4567602</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37">
+        <v>10.4</v>
+      </c>
+      <c r="F37" t="s">
+        <v>4</v>
+      </c>
+      <c r="G37" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" t="s">
+        <v>7</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>3231065</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38">
+        <v>12.6</v>
+      </c>
+      <c r="F38" t="s">
+        <v>4</v>
+      </c>
+      <c r="G38" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" t="s">
+        <v>7</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>4561901</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39">
+        <v>10.5</v>
+      </c>
+      <c r="F39" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s">
+        <v>7</v>
+      </c>
+      <c r="I39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>3136586</v>
+      </c>
+      <c r="B40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40">
+        <v>11.5</v>
+      </c>
+      <c r="F40" t="s">
+        <v>4</v>
+      </c>
+      <c r="G40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s">
+        <v>7</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>4009382</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41">
+        <v>12.1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s">
+        <v>7</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>4830655</v>
+      </c>
+      <c r="B42" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42">
+        <v>10.4</v>
+      </c>
+      <c r="F42" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s">
+        <v>7</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>4998087</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43">
+        <v>11.9</v>
+      </c>
+      <c r="F43" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>3394191</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44">
+        <v>10.4</v>
+      </c>
+      <c r="F44" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" t="s">
+        <v>7</v>
+      </c>
+      <c r="I44" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>3336543</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45">
+        <v>12.1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
+        <v>7</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>5178571</v>
+      </c>
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" t="s">
+        <v>6</v>
+      </c>
+      <c r="E46">
+        <v>11.7</v>
+      </c>
+      <c r="F46" t="s">
+        <v>4</v>
+      </c>
+      <c r="G46" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" t="s">
+        <v>7</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>3269799</v>
+      </c>
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47">
+        <v>12.9</v>
+      </c>
+      <c r="F47" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>3259308</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48">
+        <v>12.2</v>
+      </c>
+      <c r="F48" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" t="s">
+        <v>7</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>2711051</v>
+      </c>
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49">
+        <v>12.3</v>
+      </c>
+      <c r="F49" t="s">
+        <v>4</v>
+      </c>
+      <c r="G49" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>4729019</v>
+      </c>
+      <c r="B50" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50">
+        <v>11.6</v>
+      </c>
+      <c r="F50" t="s">
+        <v>4</v>
+      </c>
+      <c r="G50" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" t="s">
+        <v>7</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>5144290</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51">
+        <v>10.9</v>
+      </c>
+      <c r="F51" t="s">
+        <v>4</v>
+      </c>
+      <c r="G51" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" t="s">
+        <v>7</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>2913678</v>
+      </c>
+      <c r="B52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52">
+        <v>11.7</v>
+      </c>
+      <c r="F52" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" t="s">
+        <v>7</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>4662464</v>
+      </c>
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53">
+        <v>10.1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>4</v>
+      </c>
+      <c r="G53" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" t="s">
+        <v>7</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>3641999</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F54" t="s">
+        <v>4</v>
+      </c>
+      <c r="G54" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" t="s">
+        <v>7</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>3901702</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55">
+        <v>13</v>
+      </c>
+      <c r="F55" t="s">
+        <v>4</v>
+      </c>
+      <c r="G55" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>3841294</v>
+      </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56">
+        <v>12.9</v>
+      </c>
+      <c r="F56" t="s">
+        <v>4</v>
+      </c>
+      <c r="G56" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" t="s">
+        <v>7</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>4570286</v>
+      </c>
+      <c r="B57" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57">
+        <v>10.9</v>
+      </c>
+      <c r="F57" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" t="s">
+        <v>7</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>3146321</v>
+      </c>
+      <c r="B58" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58">
+        <v>12.5</v>
+      </c>
+      <c r="F58" t="s">
+        <v>4</v>
+      </c>
+      <c r="G58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" t="s">
+        <v>7</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>4582294</v>
+      </c>
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" t="s">
+        <v>6</v>
+      </c>
+      <c r="E59">
+        <v>11.2</v>
+      </c>
+      <c r="F59" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" t="s">
+        <v>7</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>4249499</v>
+      </c>
+      <c r="B60" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60">
+        <v>12.3</v>
+      </c>
+      <c r="F60" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" t="s">
+        <v>11</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
